--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075C72C1-9C0C-49AC-B764-9C6B63345500}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39FACF9-683B-4686-8FB0-4EBD70B37905}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
-    <sheet name="RiskAssessmentValues1" sheetId="2" r:id="rId2"/>
-    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId3"/>
+    <sheet name="OrgAssessmentValues" sheetId="4" r:id="rId2"/>
+    <sheet name="OrgAssessmentValues1" sheetId="5" r:id="rId3"/>
+    <sheet name="RiskAssessmentValues1" sheetId="2" r:id="rId4"/>
+    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId5"/>
+    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="91">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -153,6 +156,153 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Quality_Question_2__c</t>
+  </si>
+  <si>
+    <t>Quality_Question_1__c</t>
+  </si>
+  <si>
+    <t>Quality_Question_3__c</t>
+  </si>
+  <si>
+    <t>Financial_Question1__c</t>
+  </si>
+  <si>
+    <t>Financial_Question2__c</t>
+  </si>
+  <si>
+    <t>Budgetary_Question1__c</t>
+  </si>
+  <si>
+    <t>Budgetary_Question2__c</t>
+  </si>
+  <si>
+    <t>Cost_Question1__c</t>
+  </si>
+  <si>
+    <t>Cost_Question2__c</t>
+  </si>
+  <si>
+    <t>Cost_Question3__c</t>
+  </si>
+  <si>
+    <t>Audit_Question1__c</t>
+  </si>
+  <si>
+    <t>Audit_Question2__c</t>
+  </si>
+  <si>
+    <t>Audit_Question3__c</t>
+  </si>
+  <si>
+    <t>Audit_Question4__c</t>
+  </si>
+  <si>
+    <t>Organization_Question1__c</t>
+  </si>
+  <si>
+    <t>Organization_Question2__c</t>
+  </si>
+  <si>
+    <t>Organization_Question3__c</t>
+  </si>
+  <si>
+    <t>Property_Questions1__c</t>
+  </si>
+  <si>
+    <t>Property_Questions2__c</t>
+  </si>
+  <si>
+    <t>Property_Questions3__c</t>
+  </si>
+  <si>
+    <t>Procurement_Questions1__c</t>
+  </si>
+  <si>
+    <t>Procurement_Questions2__c</t>
+  </si>
+  <si>
+    <t>Monitoring_Questions1__c</t>
+  </si>
+  <si>
+    <t>Monitoring_Questions2__c</t>
+  </si>
+  <si>
+    <t>Fraud_Questions1__c</t>
+  </si>
+  <si>
+    <t>Fraud_Questions2__c</t>
+  </si>
+  <si>
+    <t>Automated - Off the shelf</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>Requests are always submitted in accordance with the schedule outlined in the grant agreement</t>
+  </si>
+  <si>
+    <t>Requests are never submitted in accordance with the schedule outlined in the grant agreement</t>
+  </si>
+  <si>
+    <t>Only fiscal staff</t>
+  </si>
+  <si>
+    <t>None of the above</t>
+  </si>
+  <si>
+    <t>All of the above</t>
+  </si>
+  <si>
+    <t>No, the organization does not claim indirect costs.</t>
+  </si>
+  <si>
+    <t>The organization has elected to except the De minimis rate.</t>
+  </si>
+  <si>
+    <t>0-8%</t>
+  </si>
+  <si>
+    <t>20% or higher</t>
+  </si>
+  <si>
+    <t>Financial Statement Audit conducted in accordance with Generally Accepted Auditing Standards (GAAS)</t>
+  </si>
+  <si>
+    <t>Not previously audited</t>
+  </si>
+  <si>
+    <t>No audit findings reported in prior audits</t>
+  </si>
+  <si>
+    <t>Corrective Action Plan fully implemented</t>
+  </si>
+  <si>
+    <t>All the audit function activities above</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Less than 20%</t>
+  </si>
+  <si>
+    <t>Over 50%</t>
+  </si>
+  <si>
+    <t>Training is provided only during employee orientation only</t>
+  </si>
+  <si>
+    <t>Training is provided at least once every two years</t>
+  </si>
+  <si>
+    <t>Training is not provided</t>
   </si>
 </sst>
 </file>
@@ -678,6 +828,631 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E933553B-F95A-4F01-B650-F128024556A7}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCCECC7-00A8-4B5C-8E26-F12B19BBAB15}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -913,7 +1688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1146,4 +1921,228 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39FACF9-683B-4686-8FB0-4EBD70B37905}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349F7015-EAEB-4061-9DA8-95BF2FDCD501}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
     <sheet name="OrgAssessmentValues" sheetId="4" r:id="rId2"/>
-    <sheet name="OrgAssessmentValues1" sheetId="5" r:id="rId3"/>
-    <sheet name="RiskAssessmentValues1" sheetId="2" r:id="rId4"/>
-    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId5"/>
-    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId6"/>
+    <sheet name="OrgAssessmentValues3" sheetId="7" r:id="rId3"/>
+    <sheet name="OrgAssessmentValues1" sheetId="5" r:id="rId4"/>
+    <sheet name="RiskAssessmentValues1" sheetId="2" r:id="rId5"/>
+    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId6"/>
+    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -293,16 +294,34 @@
     <t>Less than 20%</t>
   </si>
   <si>
-    <t>Over 50%</t>
-  </si>
-  <si>
     <t>Training is provided only during employee orientation only</t>
   </si>
   <si>
-    <t>Training is provided at least once every two years</t>
-  </si>
-  <si>
-    <t>Training is not provided</t>
+    <t>Developed in house or by consulting firm</t>
+  </si>
+  <si>
+    <t>Semi-annually</t>
+  </si>
+  <si>
+    <t>Requests are sometimes submitted in accordance with the schedule outlined in the grant agreement</t>
+  </si>
+  <si>
+    <t>Only programmatic staff</t>
+  </si>
+  <si>
+    <t>Only (a) and (b)</t>
+  </si>
+  <si>
+    <t>The organization has a State negotiated indirect cost rate</t>
+  </si>
+  <si>
+    <t>8-20%</t>
+  </si>
+  <si>
+    <t>Single Audit</t>
+  </si>
+  <si>
+    <t>Corrective Action Plan partially implemented</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1139,7 @@
         <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1131,7 +1150,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1141,6 +1160,319 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D567C1-3DF3-4A2F-81EA-BD233AA6E8B9}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1367,7 +1699,7 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1378,7 +1710,7 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1389,7 +1721,7 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1400,7 +1732,7 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1411,7 +1743,7 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1422,7 +1754,7 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1433,7 +1765,7 @@
         <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1444,7 +1776,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCCECC7-00A8-4B5C-8E26-F12B19BBAB15}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1688,7 +2020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1923,7 +2255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349F7015-EAEB-4061-9DA8-95BF2FDCD501}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD33E36-6A0A-4035-8764-A06AEEC7869D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="98">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Corrective Action Plan partially implemented</t>
+  </si>
+  <si>
+    <t>No concerns</t>
   </si>
 </sst>
 </file>
@@ -2060,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2071,7 +2074,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2082,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2093,7 +2096,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2104,7 +2107,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2115,7 +2118,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2126,7 +2129,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2159,7 +2162,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2170,7 +2173,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2181,7 +2184,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2203,7 +2206,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2214,7 +2217,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2247,11 +2250,12 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD33E36-6A0A-4035-8764-A06AEEC7869D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E7F5BA-EDF2-4017-ADB8-35948B586002}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
     <sheet name="OrgAssessmentValues" sheetId="4" r:id="rId2"/>
     <sheet name="OrgAssessmentValues3" sheetId="7" r:id="rId3"/>
     <sheet name="OrgAssessmentValues1" sheetId="5" r:id="rId4"/>
-    <sheet name="RiskAssessmentValues1" sheetId="2" r:id="rId5"/>
-    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId6"/>
-    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId7"/>
+    <sheet name="RiskAssessmentValuesyellow" sheetId="2" r:id="rId5"/>
+    <sheet name="RiskAssessmentValuesRed" sheetId="8" r:id="rId6"/>
+    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId7"/>
+    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -325,6 +326,39 @@
   </si>
   <si>
     <t>No concerns</t>
+  </si>
+  <si>
+    <t>Non-construction - $100,000 to $250,000</t>
+  </si>
+  <si>
+    <t>1-3 years</t>
+  </si>
+  <si>
+    <t>No process to track and report cash &amp; in-kind match</t>
+  </si>
+  <si>
+    <t>Expectations Not Met</t>
+  </si>
+  <si>
+    <t>Yes, three or four years ago</t>
+  </si>
+  <si>
+    <t>Single audit required but not submitted to the FAC</t>
+  </si>
+  <si>
+    <t>A site visit was completed over a year ago, but less than 3 years ago</t>
+  </si>
+  <si>
+    <t>Minor findings</t>
+  </si>
+  <si>
+    <t>Concerns</t>
+  </si>
+  <si>
+    <t>No site visits have been conducted</t>
+  </si>
+  <si>
+    <t>Corrective Action Plan implemented within 30 days</t>
   </si>
 </sst>
 </file>
@@ -1816,7 +1850,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1827,7 +1861,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1838,7 +1872,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1849,7 +1883,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1860,7 +1894,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1871,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1882,7 +1916,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1893,7 +1927,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1904,7 +1938,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1915,7 +1949,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1948,7 +1982,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1959,7 +1993,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1970,7 +2004,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1981,7 +2015,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1992,7 +2026,7 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2003,7 +2037,7 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2024,6 +2058,241 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F1390A-D12F-4F18-A1BB-7ED029060CF4}">
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2259,7 +2528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22325"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E7F5BA-EDF2-4017-ADB8-35948B586002}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF0F138-8506-4A6A-9F7A-A60E60AD94DD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="OrgAssessmentValues1" sheetId="5" r:id="rId4"/>
     <sheet name="RiskAssessmentValuesyellow" sheetId="2" r:id="rId5"/>
     <sheet name="RiskAssessmentValuesRed" sheetId="8" r:id="rId6"/>
-    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId7"/>
-    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId8"/>
+    <sheet name="Contact_Creation" sheetId="9" r:id="rId7"/>
+    <sheet name="RiskAssessmentValues" sheetId="3" r:id="rId8"/>
+    <sheet name="OrgAssessmentValues2" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="120">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -359,6 +360,39 @@
   </si>
   <si>
     <t>Corrective Action Plan implemented within 30 days</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>PatrickM</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>patrick.m@yopmail.com</t>
+  </si>
+  <si>
+    <t>UserRole__c</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>(701)-346-5555</t>
   </si>
 </sst>
 </file>
@@ -2293,6 +2327,90 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F0F804-2965-4582-8FDA-ADDB9C543F42}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{59539FA5-55C7-4CE7-ADA4-B7377500AE1A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2528,7 +2646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF0F138-8506-4A6A-9F7A-A60E60AD94DD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F197B1-D294-4CE2-B76E-B23C71C86747}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -383,9 +383,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>patrick.m@yopmail.com</t>
-  </si>
-  <si>
     <t>UserRole__c</t>
   </si>
   <si>
@@ -393,16 +390,27 @@
   </si>
   <si>
     <t>(701)-346-5555</t>
+  </si>
+  <si>
+    <t>patrick.m1@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -425,10 +433,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -436,8 +445,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -717,14 +730,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -746,7 +759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -757,7 +770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -768,7 +781,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -779,7 +792,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -790,7 +803,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -801,7 +814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -812,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -823,7 +836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -834,7 +847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -845,7 +858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -856,7 +869,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -867,7 +880,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -878,7 +891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -889,7 +902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -900,7 +913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -920,14 +933,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E933553B-F95A-4F01-B650-F128024556A7}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.796875" customWidth="1"/>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -938,7 +951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -949,7 +962,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -960,7 +973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -971,7 +984,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -982,7 +995,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -993,7 +1006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1004,7 +1017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1015,7 +1028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1026,7 +1039,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1037,7 +1050,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1048,7 +1061,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1059,7 +1072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1070,7 +1083,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1081,7 +1094,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1092,7 +1105,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1103,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1114,7 +1127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1125,7 +1138,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1136,7 +1149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1147,7 +1160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1158,7 +1171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1182,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1180,7 +1193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1191,7 +1204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1202,7 +1215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1213,7 +1226,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1233,14 +1246,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D567C1-3DF3-4A2F-81EA-BD233AA6E8B9}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.796875" customWidth="1"/>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="79.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1251,7 +1264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1262,7 +1275,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1273,7 +1286,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1297,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1295,7 +1308,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1306,7 +1319,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1317,7 +1330,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1328,7 +1341,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1339,7 +1352,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1350,7 +1363,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1361,7 +1374,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1372,7 +1385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1383,7 +1396,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1394,7 +1407,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1405,7 +1418,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1416,7 +1429,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1427,7 +1440,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1438,7 +1451,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +1462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1460,7 +1473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1495,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1504,7 +1517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1515,7 +1528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1526,7 +1539,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1546,14 +1559,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.796875" customWidth="1"/>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="79.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1575,7 +1588,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1586,7 +1599,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1597,7 +1610,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1608,7 +1621,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1619,7 +1632,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1630,7 +1643,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1641,7 +1654,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1652,7 +1665,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1663,7 +1676,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1674,7 +1687,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1685,7 +1698,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1696,7 +1709,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1707,7 +1720,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1718,7 +1731,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1729,7 +1742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1740,7 +1753,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1751,7 +1764,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1762,7 +1775,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1773,7 +1786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1784,7 +1797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1795,7 +1808,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1806,7 +1819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1817,7 +1830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1828,7 +1841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1839,7 +1852,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1858,14 +1871,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCCECC7-00A8-4B5C-8E26-F12B19BBAB15}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1876,7 +1889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1887,7 +1900,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1898,7 +1911,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1909,7 +1922,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1920,7 +1933,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1931,7 +1944,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1942,7 +1955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1953,7 +1966,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1964,7 +1977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1975,7 +1988,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1986,7 +1999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1997,7 +2010,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2008,7 +2021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2019,7 +2032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2030,7 +2043,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2041,7 +2054,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2052,7 +2065,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2063,7 +2076,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2074,7 +2087,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2094,14 +2107,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F1390A-D12F-4F18-A1BB-7ED029060CF4}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2112,7 +2125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2123,7 +2136,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2134,7 +2147,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2145,7 +2158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2156,7 +2169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2167,7 +2180,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2178,7 +2191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2189,7 +2202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2200,7 +2213,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2211,7 +2224,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2222,7 +2235,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2233,7 +2246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2244,7 +2257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2255,7 +2268,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2266,7 +2279,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2277,7 +2290,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2288,7 +2301,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2299,7 +2312,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2310,7 +2323,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2329,13 +2342,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F0F804-2965-4582-8FDA-ADDB9C543F42}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2346,7 +2359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -2357,7 +2370,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
@@ -2368,7 +2381,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
@@ -2376,29 +2389,29 @@
         <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2413,14 +2426,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2431,7 +2444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2442,7 +2455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2477,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2475,7 +2488,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2486,7 +2499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2497,7 +2510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2508,7 +2521,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2519,7 +2532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2541,7 +2554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2552,7 +2565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2563,7 +2576,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2574,7 +2587,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2585,7 +2598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2596,7 +2609,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2607,7 +2620,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2618,7 +2631,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2629,7 +2642,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2649,14 +2662,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2667,7 +2680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2678,7 +2691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2689,7 +2702,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2700,7 +2713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2711,7 +2724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2722,7 +2735,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2733,7 +2746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2744,7 +2757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2755,7 +2768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2766,7 +2779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2777,7 +2790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2788,7 +2801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2799,7 +2812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2810,7 +2823,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2821,7 +2834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2832,7 +2845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2843,7 +2856,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2854,7 +2867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F197B1-D294-4CE2-B76E-B23C71C86747}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5275E28E-8FB2-4591-86F2-669D1E008E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="122">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>patrick.m1@yopmail.com</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgement__c</t>
+  </si>
+  <si>
+    <t>Checked</t>
   </si>
 </sst>
 </file>
@@ -730,14 +736,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -759,7 +765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -770,7 +776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -781,7 +787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -792,7 +798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -803,7 +809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -814,7 +820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -825,7 +831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -836,7 +842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -847,7 +853,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -858,7 +864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -869,7 +875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -880,7 +886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -891,7 +897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -902,7 +908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -913,7 +919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -932,15 +938,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E933553B-F95A-4F01-B650-F128024556A7}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.796875" customWidth="1"/>
-    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -962,7 +968,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -973,7 +979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -984,7 +990,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -995,7 +1001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1006,7 +1012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1017,7 +1023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1028,7 +1034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1045,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1072,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1083,7 +1089,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1094,7 +1100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1105,7 +1111,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1127,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1144,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1171,7 +1177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +1188,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1193,7 +1199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1232,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1235,6 +1241,17 @@
       </c>
       <c r="C27" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1246,14 +1263,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D567C1-3DF3-4A2F-81EA-BD233AA6E8B9}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.796875" customWidth="1"/>
-    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1292,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1286,7 +1303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1297,7 +1314,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1308,7 +1325,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1319,7 +1336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1330,7 +1347,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1341,7 +1358,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1352,7 +1369,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1363,7 +1380,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1374,7 +1391,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1385,7 +1402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1396,7 +1413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1407,7 +1424,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1418,7 +1435,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1429,7 +1446,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1440,7 +1457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1451,7 +1468,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1462,7 +1479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1473,7 +1490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1484,7 +1501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1495,7 +1512,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1506,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1517,7 +1534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1528,7 +1545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1539,7 +1556,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1559,14 +1576,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.796875" customWidth="1"/>
-    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1588,7 +1605,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1599,7 +1616,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1610,7 +1627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1621,7 +1638,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1632,7 +1649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1643,7 +1660,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1654,7 +1671,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1665,7 +1682,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1676,7 +1693,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1687,7 +1704,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1698,7 +1715,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1709,7 +1726,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1720,7 +1737,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1731,7 +1748,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1742,7 +1759,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1753,7 +1770,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1764,7 +1781,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1775,7 +1792,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1786,7 +1803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1797,7 +1814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1808,7 +1825,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1819,7 +1836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1830,7 +1847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1841,7 +1858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1852,7 +1869,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1871,14 +1888,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCCECC7-00A8-4B5C-8E26-F12B19BBAB15}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1889,7 +1906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1900,7 +1917,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1911,7 +1928,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1922,7 +1939,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1933,7 +1950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1944,7 +1961,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1955,7 +1972,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1966,7 +1983,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1977,7 +1994,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1988,7 +2005,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1999,7 +2016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2010,7 +2027,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2021,7 +2038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2032,7 +2049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2043,7 +2060,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2054,7 +2071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2065,7 +2082,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2076,7 +2093,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2087,7 +2104,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2107,14 +2124,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F1390A-D12F-4F18-A1BB-7ED029060CF4}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2136,7 +2153,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2147,7 +2164,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2158,7 +2175,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2169,7 +2186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2180,7 +2197,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2191,7 +2208,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2202,7 +2219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2213,7 +2230,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2224,7 +2241,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2235,7 +2252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2246,7 +2263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2257,7 +2274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2268,7 +2285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2279,7 +2296,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2290,7 +2307,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2301,7 +2318,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2312,7 +2329,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2323,7 +2340,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2342,13 +2359,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F0F804-2965-4582-8FDA-ADDB9C543F42}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="25.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2359,7 +2376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -2370,7 +2387,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
@@ -2381,7 +2398,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
@@ -2392,7 +2409,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -2403,7 +2420,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -2426,14 +2443,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2444,7 +2461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2455,7 +2472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2466,7 +2483,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2477,7 +2494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2488,7 +2505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2499,7 +2516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2510,7 +2527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2521,7 +2538,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2532,7 +2549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2543,7 +2560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2554,7 +2571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2565,7 +2582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2576,7 +2593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2587,7 +2604,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2598,7 +2615,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2609,7 +2626,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2620,7 +2637,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2631,7 +2648,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2642,7 +2659,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2662,14 +2679,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2680,7 +2697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2691,7 +2708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2702,7 +2719,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2713,7 +2730,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2724,7 +2741,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2735,7 +2752,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2746,7 +2763,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2757,7 +2774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2768,7 +2785,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2779,7 +2796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2790,7 +2807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2801,7 +2818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2812,7 +2829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2823,7 +2840,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2834,7 +2851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2845,7 +2862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2856,7 +2873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2867,7 +2884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5275E28E-8FB2-4591-86F2-669D1E008E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFD56B0-64DA-4CF7-874C-7D17944B52A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="45" windowWidth="20355" windowHeight="10920" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="122">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1575,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -1878,6 +1878,17 @@
       </c>
       <c r="C27" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFD56B0-64DA-4CF7-874C-7D17944B52A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF1073E-B2FF-4B6F-8DCF-A080231A98D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="45" windowWidth="20355" windowHeight="10920" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="45" windowWidth="20355" windowHeight="10920" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
